--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1446,37 +1446,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88013939</v>
+        <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>92567</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1485,19 +1485,20 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Uringe, Srm</t>
+          <t>Uringeskogen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662434</v>
+        <v>662394</v>
       </c>
       <c r="R9" t="n">
-        <v>6557030</v>
+        <v>6557026</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1521,12 +1522,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,8 +1536,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1552,13 +1569,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88013939</t>
+          <t>https://artportalen.se/Sighting/136754292</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113208399</v>
+        <v>88013939</v>
       </c>
       <c r="B10" t="n">
         <v>92567</v>
@@ -1599,17 +1616,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Uringe, Uringe, Srm</t>
+          <t>Uringe, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662379</v>
+        <v>662434</v>
       </c>
       <c r="R10" t="n">
-        <v>6556996</v>
+        <v>6557030</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,12 +1650,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,16 +1681,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113208399</t>
+          <t>https://artportalen.se/Sighting/88013939</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94478309</v>
+        <v>113208399</v>
       </c>
       <c r="B11" t="n">
-        <v>57754</v>
+        <v>92567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,52 +1698,47 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102118</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Uringeskogen, Botkyrka, Srm</t>
+          <t>Uringe, Uringe, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662368</v>
+        <v>662379</v>
       </c>
       <c r="R11" t="n">
-        <v>6557006</v>
+        <v>6556996</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,22 +1762,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>02:35</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>02:35</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,27 +1782,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tiina Laantee</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tiina Laantee, Thomas Strid, Roger Kaufmann, Marie Teilmann</t>
+          <t>Thomas Strid, Tiina Laantee</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94478309</t>
+          <t>https://artportalen.se/Sighting/113208399</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>92453790</v>
+        <v>94478309</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>57754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>102118</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1835,11 +1837,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1847,14 +1845,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Botkyrka, Srm</t>
+          <t>Uringeskogen, Botkyrka, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662399</v>
+        <v>662368</v>
       </c>
       <c r="R12" t="n">
-        <v>6557017</v>
+        <v>6557006</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1881,22 +1879,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>02:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>02:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,19 +1914,19 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tiina Laantee</t>
+          <t>Tiina Laantee, Thomas Strid, Roger Kaufmann, Marie Teilmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92453790</t>
+          <t>https://artportalen.se/Sighting/94478309</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>92673596</v>
+        <v>92453790</v>
       </c>
       <c r="B13" t="n">
         <v>58327</v>
@@ -1978,14 +1976,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Uringeskogen, Botkyrka, Srm</t>
+          <t>Botkyrka, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>662518</v>
+        <v>662399</v>
       </c>
       <c r="R13" t="n">
-        <v>6557105</v>
+        <v>6557017</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,12 +2010,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,16 +2051,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92673596</t>
+          <t>https://artportalen.se/Sighting/92453790</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132007128</v>
+        <v>92673596</v>
       </c>
       <c r="B14" t="n">
-        <v>58131</v>
+        <v>58327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,16 +2068,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103023</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2082,23 +2090,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Uringeskogen, Botkyrka, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662376</v>
+        <v>662518</v>
       </c>
       <c r="R14" t="n">
-        <v>6557006</v>
+        <v>6557105</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2122,22 +2141,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,16 +2161,136 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Tiina Laantee</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Tiina Laantee</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92673596</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132007128</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hagaberg, Hagaberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>662376</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6557006</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132007128</t>
         </is>
@@ -2182,6 +2311,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>136754292</v>
       </c>
       <c r="B9" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
